--- a/generator/data/kek/kek_numerals.xlsx
+++ b/generator/data/kek/kek_numerals.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cc6ec0edc09a2fcc/Documents/GitHub/kek-sentence-generator/data/kek/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="128" documentId="8_{7A27C376-0649-4882-9513-03660077BA71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76F42C2B-687F-4CB0-806D-E4B3973B02E1}"/>
+  <xr:revisionPtr revIDLastSave="133" documentId="8_{7A27C376-0649-4882-9513-03660077BA71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F261BF3-9DBD-4F7C-A0F5-47BE0E03F269}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{3295C59A-EB9F-491C-A141-943777C1F1F2}"/>
   </bookViews>
   <sheets>
     <sheet name="semantics_numerals" sheetId="1" r:id="rId1"/>
+    <sheet name="ALL" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="559">
   <si>
     <t>lemma_kek</t>
   </si>
@@ -2262,6 +2263,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2579,10 +2584,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{843097BA-7FC7-4B22-96AF-AA524279CBCE}">
-  <dimension ref="A1:D401"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.796875" customWidth="1"/>
+    <col min="1" max="1" width="22.3984375" customWidth="1"/>
     <col min="2" max="3" width="16.73046875" customWidth="1"/>
     <col min="9" max="9" width="22.59765625" customWidth="1"/>
   </cols>
@@ -2881,6 +2886,315 @@
         <v>20</v>
       </c>
     </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9628AB22-42FF-4A6A-8D33-114F7669BDC1}">
+  <dimension ref="A1:D401"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="22.3984375" customWidth="1"/>
+    <col min="2" max="3" width="16.73046875" customWidth="1"/>
+    <col min="9" max="9" width="22.59765625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="D7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="D8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="D9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="D10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="D11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="D12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="D13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="D14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="D15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="D16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="D17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="D18">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="D19">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="D20">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="D21">
+        <v>20</v>
+      </c>
+    </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>71</v>
